--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-11_FRS_Coverage_in_BIBS_v1.1.xlsx
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>23 test cases; Conformance register: FR-UA-001 [('Conformant', 4)]; FR-UA-003 [('Conformant', 4)]; FR-UA-051 [('Partly conformant', 2)] | Walkthrough WT-A.5, WT-B.4, WT-B.7, WT-C.10, WT-C.7, WT-C.8, WT-D.1, WT-D.5</t>
+          <t>23 test cases; Conformance register: FR-UA-001 [('Conformant', 4)]; FR-UA-003 [('Conformant', 4)]; FR-UA-051 [('Partly conformant', 2)] | Walkthrough WT-A.5, WT-B.4, WT-B.7, WT-C.10, WT-C.7, WT-C.8, WT-D.1</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-UA-042 [('Partly conformant', 2)] | Walkthrough WT-B.4, WT-D.5</t>
+          <t>6 test cases; Conformance register: FR-UA-042 [('Partly conformant', 2)] | Walkthrough WT-B.4</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-UA-043 [('Partly conformant', 1)] | Walkthrough WT-B.4, WT-D.5</t>
+          <t>3 test cases; Conformance register: FR-UA-043 [('Partly conformant', 1)] | Walkthrough WT-B.4</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>12 test cases; Conformance register: FR-UA-060 [('Conformant', 2)]; FR-UA-061 [('Conformant', 1)]; FR-UA-062 [('Conformant', 1)] | Walkthrough WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>12 test cases; Conformance register: FR-UA-060 [('Conformant', 2)]; FR-UA-061 [('Conformant', 1)]; FR-UA-062 [('Conformant', 1)] | Walkthrough WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>10 test cases; Conformance register: FR-UA-060 [('Conformant', 2)]; FR-UA-061 [('Conformant', 1)]; FR-UA-062 [('Conformant', 1)] | Walkthrough WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>10 test cases; Conformance register: FR-UA-060 [('Conformant', 2)]; FR-UA-061 [('Conformant', 1)]; FR-UA-062 [('Conformant', 1)] | Walkthrough WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-UA-063 [('Conformant', 2)] | Walkthrough WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>6 test cases; Conformance register: FR-UA-063 [('Conformant', 2)] | Walkthrough WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-UA-063 [('Conformant', 2)] | Walkthrough WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>5 test cases; Conformance register: FR-UA-063 [('Conformant', 2)] | Walkthrough WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-UA-040 [('Conformant', 2)] | Walkthrough WT-B.4, WT-D.5</t>
+          <t>8 test cases; Conformance register: FR-UA-040 [('Conformant', 2)] | Walkthrough WT-B.4</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-UA-044 [('Conformant', 2)] | Walkthrough WT-B.4, WT-D.5</t>
+          <t>7 test cases; Conformance register: FR-UA-044 [('Conformant', 2)] | Walkthrough WT-B.4</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-UA-051 [('Partly conformant', 2)] | Walkthrough WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>5 test cases; Conformance register: FR-UA-051 [('Partly conformant', 2)] | Walkthrough WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>14 test cases; Conformance register: FR-UA-041 [('Partly conformant', 2)]; FR-UA-042 [('Partly conformant', 2)]; FR-UA-043 [('Partly conformant', 1)] | Walkthrough WT-B.4, WT-D.5</t>
+          <t>14 test cases; Conformance register: FR-UA-041 [('Partly conformant', 2)]; FR-UA-042 [('Partly conformant', 2)]; FR-UA-043 [('Partly conformant', 1)] | Walkthrough WT-B.4</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
